--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.96198285154721</v>
+        <v>9.093822213376422</v>
       </c>
       <c r="D2" t="n">
-        <v>57.95150973975091</v>
+        <v>9.417120332709523</v>
       </c>
       <c r="E2" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F2" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.97358346302924</v>
+        <v>8.44570731274225</v>
       </c>
       <c r="D3" t="n">
-        <v>52.78354849917288</v>
+        <v>8.577326631115593</v>
       </c>
       <c r="E3" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F3" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.99432046529484</v>
+        <v>6.174077075610412</v>
       </c>
       <c r="D4" t="n">
-        <v>37.96295018816458</v>
+        <v>6.168979405576745</v>
       </c>
       <c r="E4" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F4" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>76.97343346067332</v>
+        <v>12.50818293735941</v>
       </c>
       <c r="D5" t="n">
-        <v>52.15833699818268</v>
+        <v>8.475729762204686</v>
       </c>
       <c r="E5" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F5" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.07777580649187</v>
+        <v>3.10013856855493</v>
       </c>
       <c r="D6" t="n">
-        <v>17.49980694550316</v>
+        <v>2.843718628644264</v>
       </c>
       <c r="E6" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F6" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.32071290995358</v>
+        <v>4.277115847867457</v>
       </c>
       <c r="D7" t="n">
-        <v>24.3217268751804</v>
+        <v>3.952280617216815</v>
       </c>
       <c r="E7" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F7" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.15902893204359</v>
+        <v>7.175842201457083</v>
       </c>
       <c r="D8" t="n">
-        <v>42.20495154521628</v>
+        <v>6.858304626097645</v>
       </c>
       <c r="E8" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F8" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.92010659199815</v>
+        <v>4.0495173211997</v>
       </c>
       <c r="D9" t="n">
-        <v>23.07143547045121</v>
+        <v>3.749108263948322</v>
       </c>
       <c r="E9" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F9" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.53352841473775</v>
+        <v>7.236698367394885</v>
       </c>
       <c r="D10" t="n">
-        <v>42.34991728022089</v>
+        <v>6.881861558035895</v>
       </c>
       <c r="E10" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F10" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.37241844570313</v>
+        <v>5.585517997426758</v>
       </c>
       <c r="D11" t="n">
-        <v>32.55686927236297</v>
+        <v>5.290491256758982</v>
       </c>
       <c r="E11" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F11" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.63661200348402</v>
+        <v>7.090949450566153</v>
       </c>
       <c r="D12" t="n">
-        <v>41.51772077248518</v>
+        <v>6.746629625528842</v>
       </c>
       <c r="E12" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F12" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.12321190929568</v>
+        <v>7.332521935260548</v>
       </c>
       <c r="D13" t="n">
-        <v>41.82618441463482</v>
+        <v>6.796754967378159</v>
       </c>
       <c r="E13" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F13" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>106.0192502108448</v>
+        <v>17.22812815926227</v>
       </c>
       <c r="D14" t="n">
-        <v>82.44602538677121</v>
+        <v>13.39747912535032</v>
       </c>
       <c r="E14" t="n">
-        <v>22.27638374437918</v>
+        <v>3.619912358461617</v>
       </c>
       <c r="F14" t="n">
-        <v>16.37596001900001</v>
+        <v>2.661093503087502</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
